--- a/Result/checksun_type/自動化機台.xlsx
+++ b/Result/checksun_type/自動化機台.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>87.16</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>89.38</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>88.4</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>89.38</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>88.40000000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>196003.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>79235.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>79235.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>84864.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>113080.18</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>113080.18</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>969.8603274618799</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>196003</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>196003.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>85.64</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>89.34</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>88.35</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>89.34</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>88.34999999999999</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>60783.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>53210.0</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>53210</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>70175.6</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>112223.88</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>112223.88</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-10030.79569813701</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>60783</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>60783.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>85.3</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>89.38</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>88.46</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>89.38</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>88.45999999999999</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>24177.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>57766.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>57766.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>69287.8</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>116801.5</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>116801.5</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-10899.91874548767</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>24177</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>24177.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>85.85999999999999</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>89.57</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>88.55</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>89.56999999999999</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>88.55</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>72685.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>61052.8</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>61052.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>75834.6</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>119132.7</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>119132.7</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-7830.168857935467</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>72685</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>72685.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>86.55999999999999</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>89.62</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>88.71</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>89.62</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>88.70999999999999</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>42528.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>75082.8</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>75082.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>89412.6</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>120987.62</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>120987.62</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-8362.448702220325</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>42528</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>42528.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>87.44</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>89.54</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>88.74</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>89.54000000000001</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>88.73999999999999</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>65877.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>90493.6</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>90493.60000000001</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>107436.9</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>121235.66</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>121235.66</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-5593.082454690855</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>65877</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>65877.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>88.36</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>89.66</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>88.81</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>89.66</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>88.81</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>83565.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>87141.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>87141.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>110364.2</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>122389.8</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>122389.8</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-3938.770584838363</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>83565</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>83565.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>89.2</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>89.66</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>88.88</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>89.66</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>88.88</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>40609.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>80809.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>80809.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>109441.2</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>122815.98</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>122815.98</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-3329.940392733435</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>40609</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>40609.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>89.92</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>89.58</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>88.93</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>89.58</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>88.93000000000001</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>142835.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>90616.4</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>90616.39999999999</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>112118.4</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>125535.6</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>125535.6</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>2261.17203858553</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>142835</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>142835.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>90.9</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>89.6</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>88.99</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>88.98999999999999</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>119582.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>103742.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>103742.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>105992.7</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>125523.74</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>125523.74</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-785.0663466225815</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>119582</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>119582.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>91.32000000000001</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>89.25</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>88.97</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>88.97</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>49115.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>124380.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>124380.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>110324.3</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>127685.92</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>127685.92</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-2617.404527397666</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>49115</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>49115.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>36.94</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>37.81</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>37.98</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>37.81</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>37.98</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>110.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>0</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>0</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-27.24568040964775</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>110</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>37.27</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>37.89</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>38.05</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>37.89</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>38.05</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>112.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>0</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>0</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-22.67144669798421</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>112</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>37.6</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>37.97</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>38.12</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>37.97</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>38.12</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>0</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>0</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-11.93064118910661</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>0</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>37.85</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>38.04</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>38.16</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>38.04</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>38.16</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>370.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>0</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>0</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-11.93064118910661</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>370</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>370.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>38.1</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>38.11</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>38.22</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>38.11</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>38.22</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>0</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>0</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-50.4996837119381</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>0</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>37.96</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>38.08</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>38.25</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>38.08</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>38.25</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>0</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>0</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-50.4996837119381</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>0</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>37.88</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>38.1</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>38.26</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>38.26</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>0</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>0</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-50.4996837119381</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>0</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>37.82000000000001</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>38.06</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>38.25</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>38.06</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>38.25</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>7.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>168.0</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>168</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>163.2</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>795.94</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>795.9400000000001</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-50.4996837119381</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>7</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>7.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>37.8</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>38.06</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>38.27</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>38.06</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>38.27</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>187.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>218.8</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>218.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>170.2</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>803.34</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>803.34</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-39.70730644232614</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>187</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>187.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>37.82</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>38.06</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>38.29</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>38.06</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>38.29</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>524.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>241.4</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>241.4</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>159.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>809.72</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>809.72</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-42.15722082708305</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>524</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>524.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>37.94</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>38.1</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>38.32</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>38.32</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>44.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>144.2</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>144.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>107.6</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>832.92</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>832.92</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-80.2586263471971</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>44</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>44.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>630.2</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>694.75</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>770.74</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>694.75</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>770.74</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>95711.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>184090.0</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>184090</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>238520.8</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>625496.02</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>625496.02</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-59407.18447863078</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>95711</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>95711.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>630.2</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>701.25</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>771.56</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>701.25</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>771.5599999999999</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>181105.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>213249.4</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>213249.4</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>261286.0</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>631907.8</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>631907.8</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-54134.00295314955</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>181105</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>181105.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>631.4</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>706.0</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>772.34</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>706</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>772.34</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>135802.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>252624.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>252624</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>286992.7</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>639483.2</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>639483.2</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-53816.8863827067</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>135802</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>135802.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>641.0</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>712.35</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>773.42</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>712.35</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>773.42</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>262274.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>287562.6</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>287562.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>323456.1</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>664782.5</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>664782.5</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-46587.93819697743</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>262274</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>262274.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>657.8</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>718.95</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>774.36</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>718.95</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>774.36</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>245558.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>296429.4</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>296429.4</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>325427.2</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>674644.66</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>674644.66</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-48147.58585318638</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>245558</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>245558.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>671.6</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>725.65</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>773.56</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>725.65</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>773.5599999999999</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>241508.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>292951.6</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>292951.6</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>382000.7</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>675976.12</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>675976.12</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-46865.09729587106</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>241508</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>241508.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>686.2</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>733.3</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>772.84</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>733.3</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>772.84</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>377978.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>309322.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>309322.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>400021.6</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>677723.46</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>677723.46</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-42925.28873913951</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>377978</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>377978.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>702.8</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>740.6</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>771.72</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>740.6</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>771.72</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>310495.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>321361.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>321361.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>392151.7</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>673300.18</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>673300.1800000001</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-50385.73048883944</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>310495</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>310495.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>711.8</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>747.5</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>770.14</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>747.5</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>770.14</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>306608.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>359349.6</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>359349.6</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>389319.8</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>672018.02</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>672018.02</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-52013.69261380937</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>306608</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>306608.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>722.4</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>754.55</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>768.06</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>754.55</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>768.0599999999999</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>228169.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>354425.0</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>354425</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>390521.3</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>675976.46</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>675976.46</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-52065.25662755885</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>228169</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>228169.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>735.0</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>760.7</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>766.1</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>760.7</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>766.1</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>323363.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>471049.8</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>471049.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>445989.1</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>679269.88</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>679269.88</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-41875.26748193102</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>323363</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>323363.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>251.2</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>258.15</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>260.34</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>258.15</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>260.34</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>62122.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>91503.6</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>91503.60000000001</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>95122.9</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>231552.36</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>231552.36</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-21661.49985951927</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>62122</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>62122.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>247.8</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>259.1</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>260.86</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>259.1</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>260.86</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>38307.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>91500.4</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>91500.39999999999</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>123933.6</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>255976.44</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>255976.44</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-21118.31036702263</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>38307</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>38307.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>245.5</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>259.95</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>261.42</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>259.95</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>261.42</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>90026.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>106275.8</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>106275.8</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>135094.9</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>259308.18</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>259308.18</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-17036.49286463374</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>90026</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>90026.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>245.0</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>261.3</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>262.08</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>261.3</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>262.08</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>139398.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>107196.0</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>107196</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>134680.8</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>264270.1</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>264270.1</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-16138.20025891271</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>139398</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>139398.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>244.2</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>262.5</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>262.77</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>262.5</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>262.77</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>127665.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>106467.4</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>106467.4</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>134710.5</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>272115.22</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>272115.22</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-19568.41795577864</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>127665</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>127665.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>243.7</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>263.58</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>263.27</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>263.58</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>263.27</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>62106.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>98742.2</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>98742.2</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>131005.0</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>275852.94</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>275852.94</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>-22512.74973859498</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>62106</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>62106.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>247.1</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>265.48</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>264.0</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>265.48</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>264</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>112184.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>156366.8</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>156366.8</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>136726.2</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>286677.98</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>286677.98</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>-18890.73265195425</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>112184</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>112184.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>252.9</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>267.23</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>264.93</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>267.23</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>264.93</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>94627.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>163914.0</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>163914</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>147017.4</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>301340.44</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>301340.44</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>-18407.2535048977</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>94627</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>94627.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>257.2</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>268.9</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>265.72</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>268.9</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>265.72</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>135755.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>162165.6</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>162165.6</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>158536.6</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>327478.82</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>327478.82</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>-15178.05995535626</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>135755</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>135755.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>260.7</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>270.75</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>266.28</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>270.75</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>266.28</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>89039.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>162953.6</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>162953.6</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>168609.9</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>360844.1</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>360844.1</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>-14429.4241718915</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>89039</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>89039.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>263.7</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>272.05</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>266.43</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>272.05</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>266.43</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>350229.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>163267.8</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>163267.8</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>174802.5</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>374295.42</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>374295.42</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>-7839.322189374274</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>350229</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>350229.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>72.94000000000001</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>69.24</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>65.52</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>69.23999999999999</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>65.52</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>178663.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>174001.0</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>174001</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>104851.6</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>89175.86</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>89175.86</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>29856.46225858906</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>178663</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>178663.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>70.32000000000001</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>68.93</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>65.09</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>68.93000000000001</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>65.09</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>396446.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>146689.8</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>146689.8</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>91208.5</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>86113.58</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>86113.58</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>30954.87453540646</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>396446</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>396446.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>67.46000000000001</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>68.34</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>64.66</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>68.34</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>64.66</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>233708.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>75018.0</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>75018</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>59913.1</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>79102.24</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>79102.24000000001</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>8084.610840309673</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>233708</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>233708.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>65.72</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>67.87</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>64.25</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>67.87</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>64.25</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>34186.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>31518.6</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>31518.6</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>40955.9</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>75260.58</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>75260.58</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-7439.716254125349</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>34186</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>34186.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>65.42</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>67.68</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>63.95</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>67.68000000000001</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>63.95</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>27002.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>33515.2</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>33515.2</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>40901.1</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>74861.44</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>74861.44</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-7974.265094242335</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>27002</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>27002.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>66.16</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>67.69</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>63.67</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>67.69</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>63.67</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>42107.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>35702.2</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>35702.2</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>40591.6</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>74491.54</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>74491.53999999999</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-7683.396826757948</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>42107</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>42107.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>67.6</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>67.91</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>63.46</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>67.91</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>63.46</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>38087.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>35727.2</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>35727.2</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>41623.0</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>73848.72</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>73848.72</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-8611.856557967461</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>38087</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>38087.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>68.9</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>68.08</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>63.24</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>68.08</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>63.24</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>16211.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>44808.2</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>44808.2</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>44435.0</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>73289.38</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>73289.38</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-9199.947011196506</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>16211</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>16211.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>69.28</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>68.1</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>62.97</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>62.97</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>44169.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>50393.2</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>50393.2</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>55705.3</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>73606.48</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>73606.48</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-7367.649551123839</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>44169</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>44169.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>69.08000000000001</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>68.16</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>62.67</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>68.16</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>62.67</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>37937.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>48287.0</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>48287</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>61169.5</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>73017.84</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>73017.84</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-7482.45140990847</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>37937</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>37937.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>68.32</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>67.93</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>62.34</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>67.93000000000001</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>62.34</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>42232.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>45481.0</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>45481</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>70700.4</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>72567.84</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>72567.84</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-6711.509372104068</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>42232</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>42232.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>20.51</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>21.47</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>22.97</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>21.47</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>22.97</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>10516.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>6553.2</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>6553.2</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>6621.7</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>7055.1</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>7055.1</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>451.8476631753983</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>10516</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>10516.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>20.33</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>21.54</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>23.05</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>21.54</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>23.05</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>5964.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>5690.8</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>5690.8</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>6322.5</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>7140.5</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>7140.5</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>126.0489308279157</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>5964</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>5964.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>20.37</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>21.66</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>23.16</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>21.66</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>23.16</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>7205.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>5879.8</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>5879.8</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>5999.1</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>7311.98</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>7311.98</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>143.8347085162286</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>7205</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>7205.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>20.5</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>21.8</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>23.27</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>23.27</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>7576.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>6293.0</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>6293</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>5560.0</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>7585.92</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>7585.92</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>31.14172276681074</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>7576</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>7576.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>20.82</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>21.99</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>23.38</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>21.99</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>23.38</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>1505.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>6001.4</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>6001.4</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>5125.2</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>7728.1</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>7728.1</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-170.7104612597432</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>1505</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>1505.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>21.2</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>22.14</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>23.48</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>23.48</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>6204.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>6690.2</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>6690.2</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>5272.2</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>8019.26</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>8019.26</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>197.4903637473135</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>6204</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>6204.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>21.64</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>22.28</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>23.6</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>22.28</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>23.6</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>6909.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>6954.2</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>6954.2</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>5247.3</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>8221.3</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>8221.299999999999</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>212.9740293378472</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>6909</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>6909.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>21.92</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>22.38</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>23.71</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>22.38</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>23.71</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>9271.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>6118.4</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>6118.4</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>5174.1</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>8359.92</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>8359.92</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>151.9516219908282</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>9271</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>9271.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>22.07</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>22.46</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>23.8</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>22.46</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>23.8</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>6118.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>4827.0</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>4827</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>4621.6</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>8529.86</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>8529.860000000001</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-193.7215178617271</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>6118</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>6118.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>22.18</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>22.52</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>23.89</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>23.89</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>4949.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>4249.0</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>4249</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>4420.6</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>8793.4</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>8793.4</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-342.8002348703167</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>4949</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>4949.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>22.07</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>22.52</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>23.99</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>22.52</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>23.99</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>7524.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>3854.2</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>3854.2</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>4442.4</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>9497.76</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>9497.76</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-418.2769650657883</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>7524</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>7524.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>18.01</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>18.55</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>19.23</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>18.55</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>19.23</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>1267.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>929.4</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>929.4</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>1477.7</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>1615.24</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>1615.24</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-113.9833348936809</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>1267</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>1267.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>18.03</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>18.6</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>19.27</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>19.27</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>938.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>1032.8</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>1032.8</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>1454.5</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>1633.92</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>1633.92</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-129.3213470370649</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>938</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>938.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>18.06</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>18.67</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>19.31</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>18.67</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>19.31</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>456.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>1421.2</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>1421.2</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>1522.3</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>1648.04</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>1648.04</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-111.3641734191469</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>456</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>456.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>18.11</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>18.75</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>19.36</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>19.36</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>1015.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>1799.6</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>1799.6</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>1812.4</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>1720.44</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>1720.44</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-30.09091920000878</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>1015</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>1015.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>18.25</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>18.84</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>19.42</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>18.84</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>19.42</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>971.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>1795.8</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>1795.8</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>1873.7</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>1786.08</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>1786.08</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>27.19554822733176</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>971</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>971.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>18.31</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>18.9</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>19.47</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>19.47</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>1784.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>2026.0</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>2026</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>1876.4</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>1842.62</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>1842.62</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>112.7763749725561</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>1784</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>1784.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>18.43</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>18.97</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>19.52</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>18.97</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>19.52</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>2880.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>1876.2</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>1876.2</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>1779.1</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>1829.1</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>1829.1</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>143.8998283595713</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>2880</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>2880.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>18.54</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>19.04</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>19.56</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>19.04</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>19.56</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>2348.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>1623.4</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>1623.4</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>1839.5</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>1781.6</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>1781.6</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>65.79405361389377</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>2348</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>2348.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>18.67</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>19.1</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>19.6</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>19.6</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>996.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>1825.2</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>1825.2</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>1668.7</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>1769.68</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>1769.68</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>8.86458777671578</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>996</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>996.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>18.77</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>19.15</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>19.63</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>19.15</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>19.63</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>2122.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>1951.6</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>1951.6</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>1698.3</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>1778.96</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>1778.96</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>72.07732987443546</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>2122</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>2122.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>18.86</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>19.2</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>19.67</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>19.67</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>1035.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>1726.8</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>1726.8</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>1601.0</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>1803.6</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>1803.6</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>39.16419966137687</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>1035</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>1035.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
@@ -34445,7 +33983,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -34629,15 +34167,11 @@
           <t>19.45</t>
         </is>
       </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>20.26</t>
-        </is>
-      </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>21.48</t>
-        </is>
+      <c r="AM79" t="n">
+        <v>20.26</v>
+      </c>
+      <c r="AN79" t="n">
+        <v>21.48</v>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
@@ -34684,20 +34218,16 @@
           <t>446.0</t>
         </is>
       </c>
-      <c r="AX79" t="inlineStr">
-        <is>
-          <t>537.2</t>
-        </is>
+      <c r="AX79" t="n">
+        <v>537.2</v>
       </c>
       <c r="AY79" t="inlineStr">
         <is>
           <t>724.2</t>
         </is>
       </c>
-      <c r="AZ79" t="inlineStr">
-        <is>
-          <t>1332.24</t>
-        </is>
+      <c r="AZ79" t="n">
+        <v>1332.24</v>
       </c>
       <c r="BA79" t="inlineStr">
         <is>
@@ -34714,8 +34244,10 @@
           <t>-141.0385748025855</t>
         </is>
       </c>
-      <c r="BD79" t="n">
-        <v>446</v>
+      <c r="BD79" t="inlineStr">
+        <is>
+          <t>446.0</t>
+        </is>
       </c>
       <c r="BE79" t="inlineStr">
         <is>
@@ -34881,7 +34413,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -35065,15 +34597,11 @@
           <t>19.31</t>
         </is>
       </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>20.36</t>
-        </is>
-      </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>21.54</t>
-        </is>
+      <c r="AM80" t="n">
+        <v>20.36</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>21.54</v>
       </c>
       <c r="AO80" t="inlineStr">
         <is>
@@ -35120,20 +34648,16 @@
           <t>166.0</t>
         </is>
       </c>
-      <c r="AX80" t="inlineStr">
-        <is>
-          <t>494.2</t>
-        </is>
+      <c r="AX80" t="n">
+        <v>494.2</v>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
           <t>754.3</t>
         </is>
       </c>
-      <c r="AZ80" t="inlineStr">
-        <is>
-          <t>1394.4</t>
-        </is>
+      <c r="AZ80" t="n">
+        <v>1394.4</v>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
@@ -35150,8 +34674,10 @@
           <t>-143.6359791514134</t>
         </is>
       </c>
-      <c r="BD80" t="n">
-        <v>166</v>
+      <c r="BD80" t="inlineStr">
+        <is>
+          <t>166.0</t>
+        </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
@@ -35317,7 +34843,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -35501,15 +35027,11 @@
           <t>19.25</t>
         </is>
       </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>20.49</t>
-        </is>
-      </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>21.61</t>
-        </is>
+      <c r="AM81" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="AN81" t="n">
+        <v>21.61</v>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
@@ -35556,20 +35078,16 @@
           <t>290.0</t>
         </is>
       </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>804.0</t>
-        </is>
+      <c r="AX81" t="n">
+        <v>804</v>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
           <t>822.2</t>
         </is>
       </c>
-      <c r="AZ81" t="inlineStr">
-        <is>
-          <t>1439.06</t>
-        </is>
+      <c r="AZ81" t="n">
+        <v>1439.06</v>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
@@ -35586,8 +35104,10 @@
           <t>-112.2167003943315</t>
         </is>
       </c>
-      <c r="BD81" t="n">
-        <v>290</v>
+      <c r="BD81" t="inlineStr">
+        <is>
+          <t>290.0</t>
+        </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
@@ -35753,7 +35273,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35937,15 +35457,11 @@
           <t>19.42</t>
         </is>
       </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>20.64</t>
-        </is>
-      </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>21.68</t>
-        </is>
+      <c r="AM82" t="n">
+        <v>20.64</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>21.68</v>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
@@ -35992,20 +35508,16 @@
           <t>1287.0</t>
         </is>
       </c>
-      <c r="AX82" t="inlineStr">
-        <is>
-          <t>930.4</t>
-        </is>
+      <c r="AX82" t="n">
+        <v>930.4</v>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
           <t>895.9</t>
         </is>
       </c>
-      <c r="AZ82" t="inlineStr">
-        <is>
-          <t>1833.62</t>
-        </is>
+      <c r="AZ82" t="n">
+        <v>1833.62</v>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
@@ -36022,8 +35534,10 @@
           <t>-76.60999144155971</t>
         </is>
       </c>
-      <c r="BD82" t="n">
-        <v>1287</v>
+      <c r="BD82" t="inlineStr">
+        <is>
+          <t>1287.0</t>
+        </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
@@ -36189,7 +35703,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -36373,15 +35887,11 @@
           <t>19.67</t>
         </is>
       </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>20.79</t>
-        </is>
-      </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>21.75</t>
-        </is>
+      <c r="AM83" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>21.75</v>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
@@ -36428,20 +35938,16 @@
           <t>497.0</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
-        <is>
-          <t>738.2</t>
-        </is>
+      <c r="AX83" t="n">
+        <v>738.2</v>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
           <t>769.3</t>
         </is>
       </c>
-      <c r="AZ83" t="inlineStr">
-        <is>
-          <t>1851.22</t>
-        </is>
+      <c r="AZ83" t="n">
+        <v>1851.22</v>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
@@ -36458,8 +35964,10 @@
           <t>-129.8286218146873</t>
         </is>
       </c>
-      <c r="BD83" t="n">
-        <v>497</v>
+      <c r="BD83" t="inlineStr">
+        <is>
+          <t>497.0</t>
+        </is>
       </c>
       <c r="BE83" t="inlineStr">
         <is>
@@ -36625,7 +36133,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36809,15 +36317,11 @@
           <t>19.86</t>
         </is>
       </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>20.94</t>
-        </is>
-      </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>21.81</t>
-        </is>
+      <c r="AM84" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="AN84" t="n">
+        <v>21.81</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -36864,20 +36368,16 @@
           <t>231.0</t>
         </is>
       </c>
-      <c r="AX84" t="inlineStr">
-        <is>
-          <t>911.2</t>
-        </is>
+      <c r="AX84" t="n">
+        <v>911.2</v>
       </c>
       <c r="AY84" t="inlineStr">
         <is>
           <t>794.5</t>
         </is>
       </c>
-      <c r="AZ84" t="inlineStr">
-        <is>
-          <t>1867.82</t>
-        </is>
+      <c r="AZ84" t="n">
+        <v>1867.82</v>
       </c>
       <c r="BA84" t="inlineStr">
         <is>
@@ -36894,8 +36394,10 @@
           <t>-116.5756429972018</t>
         </is>
       </c>
-      <c r="BD84" t="n">
-        <v>231</v>
+      <c r="BD84" t="inlineStr">
+        <is>
+          <t>231.0</t>
+        </is>
       </c>
       <c r="BE84" t="inlineStr">
         <is>
@@ -37061,7 +36563,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -37245,15 +36747,11 @@
           <t>20.17</t>
         </is>
       </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>21.1</t>
-        </is>
-      </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>21.86</t>
-        </is>
+      <c r="AM85" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>21.86</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -37300,20 +36798,16 @@
           <t>1715.0</t>
         </is>
       </c>
-      <c r="AX85" t="inlineStr">
-        <is>
-          <t>1014.4</t>
-        </is>
+      <c r="AX85" t="n">
+        <v>1014.4</v>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
           <t>834.8</t>
         </is>
       </c>
-      <c r="AZ85" t="inlineStr">
-        <is>
-          <t>1896.36</t>
-        </is>
+      <c r="AZ85" t="n">
+        <v>1896.36</v>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
@@ -37330,8 +36824,10 @@
           <t>-64.97940029375127</t>
         </is>
       </c>
-      <c r="BD85" t="n">
-        <v>1715</v>
+      <c r="BD85" t="inlineStr">
+        <is>
+          <t>1715.0</t>
+        </is>
       </c>
       <c r="BE85" t="inlineStr">
         <is>
@@ -37497,7 +36993,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -37681,15 +37177,11 @@
           <t>20.44</t>
         </is>
       </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>21.27</t>
-        </is>
-      </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>21.92</t>
-        </is>
+      <c r="AM86" t="n">
+        <v>21.27</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>21.92</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -37736,20 +37228,16 @@
           <t>922.0</t>
         </is>
       </c>
-      <c r="AX86" t="inlineStr">
-        <is>
-          <t>840.4</t>
-        </is>
+      <c r="AX86" t="n">
+        <v>840.4</v>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
           <t>714.3</t>
         </is>
       </c>
-      <c r="AZ86" t="inlineStr">
-        <is>
-          <t>1889.2</t>
-        </is>
+      <c r="AZ86" t="n">
+        <v>1889.2</v>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
@@ -37766,8 +37254,10 @@
           <t>-147.9497892783307</t>
         </is>
       </c>
-      <c r="BD86" t="n">
-        <v>922</v>
+      <c r="BD86" t="inlineStr">
+        <is>
+          <t>922.0</t>
+        </is>
       </c>
       <c r="BE86" t="inlineStr">
         <is>
@@ -37933,7 +37423,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -38117,15 +37607,11 @@
           <t>20.46</t>
         </is>
       </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>21.43</t>
-        </is>
-      </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>21.96</t>
-        </is>
+      <c r="AM87" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>21.96</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -38172,20 +37658,16 @@
           <t>326.0</t>
         </is>
       </c>
-      <c r="AX87" t="inlineStr">
-        <is>
-          <t>861.4</t>
-        </is>
+      <c r="AX87" t="n">
+        <v>861.4</v>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
           <t>702.8</t>
         </is>
       </c>
-      <c r="AZ87" t="inlineStr">
-        <is>
-          <t>2075.44</t>
-        </is>
+      <c r="AZ87" t="n">
+        <v>2075.44</v>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
@@ -38202,8 +37684,10 @@
           <t>-176.2307096392179</t>
         </is>
       </c>
-      <c r="BD87" t="n">
-        <v>326</v>
+      <c r="BD87" t="inlineStr">
+        <is>
+          <t>326.0</t>
+        </is>
       </c>
       <c r="BE87" t="inlineStr">
         <is>
@@ -38369,7 +37853,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -38553,15 +38037,11 @@
           <t>20.53</t>
         </is>
       </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>21.46</t>
-        </is>
-      </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>22.01</t>
-        </is>
+      <c r="AM88" t="n">
+        <v>21.46</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>22.01</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -38608,20 +38088,16 @@
           <t>1362.0</t>
         </is>
       </c>
-      <c r="AX88" t="inlineStr">
-        <is>
-          <t>800.4</t>
-        </is>
+      <c r="AX88" t="n">
+        <v>800.4</v>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
           <t>791.6</t>
         </is>
       </c>
-      <c r="AZ88" t="inlineStr">
-        <is>
-          <t>2169.22</t>
-        </is>
+      <c r="AZ88" t="n">
+        <v>2169.22</v>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
@@ -38638,8 +38114,10 @@
           <t>-146.4809276676563</t>
         </is>
       </c>
-      <c r="BD88" t="n">
-        <v>1362</v>
+      <c r="BD88" t="inlineStr">
+        <is>
+          <t>1362.0</t>
+        </is>
       </c>
       <c r="BE88" t="inlineStr">
         <is>
@@ -38805,7 +38283,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -38989,15 +38467,11 @@
           <t>20.6</t>
         </is>
       </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>21.49</t>
-        </is>
-      </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>22.08</t>
-        </is>
+      <c r="AM89" t="n">
+        <v>21.49</v>
+      </c>
+      <c r="AN89" t="n">
+        <v>22.08</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -39044,20 +38518,16 @@
           <t>747.0</t>
         </is>
       </c>
-      <c r="AX89" t="inlineStr">
-        <is>
-          <t>677.8</t>
-        </is>
+      <c r="AX89" t="n">
+        <v>677.8</v>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
           <t>999.4</t>
         </is>
       </c>
-      <c r="AZ89" t="inlineStr">
-        <is>
-          <t>2614.76</t>
-        </is>
+      <c r="AZ89" t="n">
+        <v>2614.76</v>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
@@ -39074,8 +38544,10 @@
           <t>-209.7497774344375</t>
         </is>
       </c>
-      <c r="BD89" t="n">
-        <v>747</v>
+      <c r="BD89" t="inlineStr">
+        <is>
+          <t>747.0</t>
+        </is>
       </c>
       <c r="BE89" t="inlineStr">
         <is>
@@ -39241,7 +38713,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -39425,15 +38897,11 @@
           <t>53.76000000000001</t>
         </is>
       </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>56.08</t>
-        </is>
-      </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>68.33</t>
-        </is>
+      <c r="AM90" t="n">
+        <v>56.08</v>
+      </c>
+      <c r="AN90" t="n">
+        <v>68.33</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -39480,20 +38948,16 @@
           <t>24597.0</t>
         </is>
       </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>11970.4</t>
-        </is>
+      <c r="AX90" t="n">
+        <v>11970.4</v>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
           <t>14410.4</t>
         </is>
       </c>
-      <c r="AZ90" t="inlineStr">
-        <is>
-          <t>60582.04</t>
-        </is>
+      <c r="AZ90" t="n">
+        <v>60582.04</v>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
@@ -39510,8 +38974,10 @@
           <t>-2061.16291586608</t>
         </is>
       </c>
-      <c r="BD90" t="n">
-        <v>24597</v>
+      <c r="BD90" t="inlineStr">
+        <is>
+          <t>24597.0</t>
+        </is>
       </c>
       <c r="BE90" t="inlineStr">
         <is>
@@ -39677,7 +39143,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39861,15 +39327,11 @@
           <t>52.76000000000001</t>
         </is>
       </c>
-      <c r="AM91" t="inlineStr">
-        <is>
-          <t>56.23</t>
-        </is>
-      </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>69.22</t>
-        </is>
+      <c r="AM91" t="n">
+        <v>56.23</v>
+      </c>
+      <c r="AN91" t="n">
+        <v>69.22</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -39916,20 +39378,16 @@
           <t>7606.0</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
-        <is>
-          <t>10362.6</t>
-        </is>
+      <c r="AX91" t="n">
+        <v>10362.6</v>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
           <t>13274.1</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
-        <is>
-          <t>63574.72</t>
-        </is>
+      <c r="AZ91" t="n">
+        <v>63574.72</v>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
@@ -39946,8 +39404,10 @@
           <t>-3409.033025106773</t>
         </is>
       </c>
-      <c r="BD91" t="n">
-        <v>7606</v>
+      <c r="BD91" t="inlineStr">
+        <is>
+          <t>7606.0</t>
+        </is>
       </c>
       <c r="BE91" t="inlineStr">
         <is>
@@ -40113,7 +39573,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -40297,15 +39757,11 @@
           <t>52.77999999999999</t>
         </is>
       </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>56.58</t>
-        </is>
-      </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>70.33</t>
-        </is>
+      <c r="AM92" t="n">
+        <v>56.58</v>
+      </c>
+      <c r="AN92" t="n">
+        <v>70.33</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -40352,20 +39808,16 @@
           <t>5735.0</t>
         </is>
       </c>
-      <c r="AX92" t="inlineStr">
-        <is>
-          <t>15118.2</t>
-        </is>
+      <c r="AX92" t="n">
+        <v>15118.2</v>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
           <t>14353.4</t>
         </is>
       </c>
-      <c r="AZ92" t="inlineStr">
-        <is>
-          <t>66631.6</t>
-        </is>
+      <c r="AZ92" t="n">
+        <v>66631.60000000001</v>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
@@ -40382,8 +39834,10 @@
           <t>-3392.346287411092</t>
         </is>
       </c>
-      <c r="BD92" t="n">
-        <v>5735</v>
+      <c r="BD92" t="inlineStr">
+        <is>
+          <t>5735.0</t>
+        </is>
       </c>
       <c r="BE92" t="inlineStr">
         <is>
@@ -40549,7 +40003,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40733,15 +40187,11 @@
           <t>53.02</t>
         </is>
       </c>
-      <c r="AM93" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
-      </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>71.28</t>
-        </is>
+      <c r="AM93" t="n">
+        <v>57</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>71.28</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
@@ -40788,20 +40238,16 @@
           <t>8395.0</t>
         </is>
       </c>
-      <c r="AX93" t="inlineStr">
-        <is>
-          <t>15847.8</t>
-        </is>
+      <c r="AX93" t="n">
+        <v>15847.8</v>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
           <t>14792.0</t>
         </is>
       </c>
-      <c r="AZ93" t="inlineStr">
-        <is>
-          <t>67675.16</t>
-        </is>
+      <c r="AZ93" t="n">
+        <v>67675.16</v>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
@@ -40818,8 +40264,10 @@
           <t>-3046.888580438288</t>
         </is>
       </c>
-      <c r="BD93" t="n">
-        <v>8395</v>
+      <c r="BD93" t="inlineStr">
+        <is>
+          <t>8395.0</t>
+        </is>
       </c>
       <c r="BE93" t="inlineStr">
         <is>
@@ -40985,7 +40433,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -41169,15 +40617,11 @@
           <t>53.62</t>
         </is>
       </c>
-      <c r="AM94" t="inlineStr">
-        <is>
-          <t>57.46</t>
-        </is>
-      </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>72.25</t>
-        </is>
+      <c r="AM94" t="n">
+        <v>57.46</v>
+      </c>
+      <c r="AN94" t="n">
+        <v>72.25</v>
       </c>
       <c r="AO94" t="inlineStr">
         <is>
@@ -41224,20 +40668,16 @@
           <t>13519.0</t>
         </is>
       </c>
-      <c r="AX94" t="inlineStr">
-        <is>
-          <t>17459.4</t>
-        </is>
+      <c r="AX94" t="n">
+        <v>17459.4</v>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
           <t>15888.6</t>
         </is>
       </c>
-      <c r="AZ94" t="inlineStr">
-        <is>
-          <t>68698.78</t>
-        </is>
+      <c r="AZ94" t="n">
+        <v>68698.78</v>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
@@ -41254,8 +40694,10 @@
           <t>-2729.560121175775</t>
         </is>
       </c>
-      <c r="BD94" t="n">
-        <v>13519</v>
+      <c r="BD94" t="inlineStr">
+        <is>
+          <t>13519.0</t>
+        </is>
       </c>
       <c r="BE94" t="inlineStr">
         <is>
@@ -41421,7 +40863,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -41605,15 +41047,11 @@
           <t>54.04000000000001</t>
         </is>
       </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>57.81</t>
-        </is>
-      </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>73.24</t>
-        </is>
+      <c r="AM95" t="n">
+        <v>57.81</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>73.23999999999999</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -41660,20 +41098,16 @@
           <t>16558.0</t>
         </is>
       </c>
-      <c r="AX95" t="inlineStr">
-        <is>
-          <t>16850.4</t>
-        </is>
+      <c r="AX95" t="n">
+        <v>16850.4</v>
       </c>
       <c r="AY95" t="inlineStr">
         <is>
           <t>16629.5</t>
         </is>
       </c>
-      <c r="AZ95" t="inlineStr">
-        <is>
-          <t>69309.46</t>
-        </is>
+      <c r="AZ95" t="n">
+        <v>69309.46000000001</v>
       </c>
       <c r="BA95" t="inlineStr">
         <is>
@@ -41690,8 +41124,10 @@
           <t>-2727.749460758765</t>
         </is>
       </c>
-      <c r="BD95" t="n">
-        <v>16558</v>
+      <c r="BD95" t="inlineStr">
+        <is>
+          <t>16558.0</t>
+        </is>
       </c>
       <c r="BE95" t="inlineStr">
         <is>
@@ -41857,7 +41293,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -42041,15 +41477,11 @@
           <t>54.84</t>
         </is>
       </c>
-      <c r="AM96" t="inlineStr">
-        <is>
-          <t>58.33</t>
-        </is>
-      </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>74.18</t>
-        </is>
+      <c r="AM96" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="AN96" t="n">
+        <v>74.18000000000001</v>
       </c>
       <c r="AO96" t="inlineStr">
         <is>
@@ -42096,20 +41528,16 @@
           <t>31384.0</t>
         </is>
       </c>
-      <c r="AX96" t="inlineStr">
-        <is>
-          <t>16185.6</t>
-        </is>
+      <c r="AX96" t="n">
+        <v>16185.6</v>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
           <t>16742.4</t>
         </is>
       </c>
-      <c r="AZ96" t="inlineStr">
-        <is>
-          <t>70346.4</t>
-        </is>
+      <c r="AZ96" t="n">
+        <v>70346.39999999999</v>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
@@ -42126,8 +41554,10 @@
           <t>-2953.350322278795</t>
         </is>
       </c>
-      <c r="BD96" t="n">
-        <v>31384</v>
+      <c r="BD96" t="inlineStr">
+        <is>
+          <t>31384.0</t>
+        </is>
       </c>
       <c r="BE96" t="inlineStr">
         <is>
@@ -42293,7 +41723,7 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -42477,15 +41907,11 @@
           <t>55.22000000000001</t>
         </is>
       </c>
-      <c r="AM97" t="inlineStr">
-        <is>
-          <t>58.77</t>
-        </is>
-      </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>75.18</t>
-        </is>
+      <c r="AM97" t="n">
+        <v>58.77</v>
+      </c>
+      <c r="AN97" t="n">
+        <v>75.18000000000001</v>
       </c>
       <c r="AO97" t="inlineStr">
         <is>
@@ -42532,20 +41958,16 @@
           <t>9383.0</t>
         </is>
       </c>
-      <c r="AX97" t="inlineStr">
-        <is>
-          <t>13588.6</t>
-        </is>
+      <c r="AX97" t="n">
+        <v>13588.6</v>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
           <t>15363.1</t>
         </is>
       </c>
-      <c r="AZ97" t="inlineStr">
-        <is>
-          <t>71262.88</t>
-        </is>
+      <c r="AZ97" t="n">
+        <v>71262.88</v>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
@@ -42562,8 +41984,10 @@
           <t>-4758.660470083167</t>
         </is>
       </c>
-      <c r="BD97" t="n">
-        <v>9383</v>
+      <c r="BD97" t="inlineStr">
+        <is>
+          <t>9383.0</t>
+        </is>
       </c>
       <c r="BE97" t="inlineStr">
         <is>
@@ -42729,7 +42153,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -42913,15 +42337,11 @@
           <t>56.0</t>
         </is>
       </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>59.2</t>
-        </is>
-      </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>76.08</t>
-        </is>
+      <c r="AM98" t="n">
+        <v>59.2</v>
+      </c>
+      <c r="AN98" t="n">
+        <v>76.08</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -42968,20 +42388,16 @@
           <t>16453.0</t>
         </is>
       </c>
-      <c r="AX98" t="inlineStr">
-        <is>
-          <t>13736.2</t>
-        </is>
+      <c r="AX98" t="n">
+        <v>13736.2</v>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
           <t>16612.6</t>
         </is>
       </c>
-      <c r="AZ98" t="inlineStr">
-        <is>
-          <t>73107.78</t>
-        </is>
+      <c r="AZ98" t="n">
+        <v>73107.78</v>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
@@ -42998,8 +42414,10 @@
           <t>-4810.472807300728</t>
         </is>
       </c>
-      <c r="BD98" t="n">
-        <v>16453</v>
+      <c r="BD98" t="inlineStr">
+        <is>
+          <t>16453.0</t>
+        </is>
       </c>
       <c r="BE98" t="inlineStr">
         <is>
@@ -43165,7 +42583,7 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -43349,15 +42767,11 @@
           <t>56.5</t>
         </is>
       </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>59.74</t>
-        </is>
-      </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>77.0</t>
-        </is>
+      <c r="AM99" t="n">
+        <v>59.74</v>
+      </c>
+      <c r="AN99" t="n">
+        <v>77</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
@@ -43404,20 +42818,16 @@
           <t>10474.0</t>
         </is>
       </c>
-      <c r="AX99" t="inlineStr">
-        <is>
-          <t>14317.8</t>
-        </is>
+      <c r="AX99" t="n">
+        <v>14317.8</v>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
           <t>19385.9</t>
         </is>
       </c>
-      <c r="AZ99" t="inlineStr">
-        <is>
-          <t>75113.48</t>
-        </is>
+      <c r="AZ99" t="n">
+        <v>75113.48</v>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
@@ -43434,8 +42844,10 @@
           <t>-5470.187831636504</t>
         </is>
       </c>
-      <c r="BD99" t="n">
-        <v>10474</v>
+      <c r="BD99" t="inlineStr">
+        <is>
+          <t>10474.0</t>
+        </is>
       </c>
       <c r="BE99" t="inlineStr">
         <is>
@@ -43601,7 +43013,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -43785,15 +43197,11 @@
           <t>56.78000000000001</t>
         </is>
       </c>
-      <c r="AM100" t="inlineStr">
-        <is>
-          <t>60.15</t>
-        </is>
-      </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>78.03</t>
-        </is>
+      <c r="AM100" t="n">
+        <v>60.15</v>
+      </c>
+      <c r="AN100" t="n">
+        <v>78.03</v>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
@@ -43840,20 +43248,16 @@
           <t>13234.0</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
-        <is>
-          <t>16408.6</t>
-        </is>
+      <c r="AX100" t="n">
+        <v>16408.6</v>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
           <t>19907.5</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
-        <is>
-          <t>92155.28</t>
-        </is>
+      <c r="AZ100" t="n">
+        <v>92155.28</v>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
@@ -43870,8 +43274,10 @@
           <t>-5576.66687241488</t>
         </is>
       </c>
-      <c r="BD100" t="n">
-        <v>13234</v>
+      <c r="BD100" t="inlineStr">
+        <is>
+          <t>13234.0</t>
+        </is>
       </c>
       <c r="BE100" t="inlineStr">
         <is>
